--- a/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_จันทบุรี_ปีงบ69.xlsx
+++ b/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_จันทบุรี_ปีงบ69.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Report" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$M$106</definedName>
+    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$N$106</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
   <si>
     <t xml:space="preserve">รายงานการตรวจวัดค่าแรงดันน้ำ</t>
   </si>
@@ -322,6 +322,48 @@
         <family val="2"/>
         <charset val="222"/>
       </rPr>
+      <t xml:space="preserve">เม</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">ย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">. 69</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
       <t xml:space="preserve">ก</t>
     </r>
     <r>
@@ -6931,7 +6973,7 @@
     <t xml:space="preserve">พิมพ์รายงานวันที่</t>
   </si>
   <si>
-    <t xml:space="preserve">4/3/2569</t>
+    <t xml:space="preserve">3/4/2569</t>
   </si>
   <si>
     <t xml:space="preserve">หน้าที่</t>
@@ -7144,7 +7186,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V111"/>
+  <dimension ref="A1:W111"/>
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.6"/>
@@ -7158,15 +7200,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="3.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="23.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="1.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="1.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="5.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="0.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="7.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="1.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="5.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="0.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="2.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7188,11 +7231,12 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
@@ -7213,11 +7257,12 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
@@ -7238,11 +7283,12 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
@@ -7258,6 +7304,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -7292,6 +7339,9 @@
       </c>
       <c r="M5" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7308,13 +7358,14 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -7338,9 +7389,12 @@
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7349,7 +7403,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -7373,9 +7427,12 @@
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7384,7 +7441,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -7408,9 +7465,12 @@
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7419,7 +7479,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -7443,9 +7503,12 @@
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7454,7 +7517,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -7478,9 +7541,12 @@
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7489,7 +7555,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -7513,9 +7579,12 @@
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7524,7 +7593,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -7548,9 +7617,12 @@
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7559,7 +7631,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -7583,9 +7655,12 @@
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7594,7 +7669,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -7618,9 +7693,12 @@
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7629,7 +7707,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -7653,9 +7731,12 @@
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7664,7 +7745,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -7688,9 +7769,12 @@
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7699,7 +7783,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -7723,9 +7807,12 @@
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7734,7 +7821,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -7758,9 +7845,12 @@
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7769,7 +7859,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -7793,9 +7883,12 @@
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7804,7 +7897,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -7828,9 +7921,12 @@
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7839,7 +7935,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -7863,9 +7959,12 @@
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7874,7 +7973,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -7898,9 +7997,12 @@
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7909,12 +8011,12 @@
         <v>18</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="7" t="n">
-        <v>0.7</v>
+        <v>0.733333</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>0.7</v>
@@ -7933,9 +8035,12 @@
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7944,7 +8049,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -7968,9 +8073,12 @@
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7979,7 +8087,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -8003,9 +8111,12 @@
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8014,7 +8125,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -8038,9 +8149,12 @@
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8049,7 +8163,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -8073,9 +8187,12 @@
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8084,7 +8201,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -8108,9 +8225,12 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8119,7 +8239,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -8143,9 +8263,12 @@
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8154,7 +8277,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -8178,9 +8301,12 @@
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8189,7 +8315,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -8213,9 +8339,12 @@
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8224,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -8248,9 +8377,12 @@
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8259,7 +8391,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -8283,9 +8415,12 @@
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8294,7 +8429,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -8318,9 +8453,12 @@
       </c>
       <c r="K35" s="9"/>
       <c r="L35" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8329,7 +8467,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -8353,9 +8491,12 @@
       </c>
       <c r="K36" s="9"/>
       <c r="L36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8364,7 +8505,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -8388,9 +8529,12 @@
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8399,7 +8543,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -8423,9 +8567,12 @@
       </c>
       <c r="K38" s="9"/>
       <c r="L38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8434,7 +8581,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -8458,9 +8605,12 @@
       </c>
       <c r="K39" s="9"/>
       <c r="L39" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8469,7 +8619,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -8493,9 +8643,12 @@
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8504,7 +8657,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -8528,9 +8681,12 @@
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8539,7 +8695,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -8563,9 +8719,12 @@
       </c>
       <c r="K42" s="9"/>
       <c r="L42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8574,7 +8733,7 @@
         <v>37</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -8598,9 +8757,12 @@
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8609,7 +8771,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -8633,9 +8795,12 @@
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8644,7 +8809,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -8668,9 +8833,12 @@
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8679,7 +8847,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -8703,9 +8871,12 @@
       </c>
       <c r="K46" s="9"/>
       <c r="L46" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8714,7 +8885,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -8738,9 +8909,12 @@
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8749,7 +8923,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
@@ -8773,9 +8947,12 @@
       </c>
       <c r="K48" s="9"/>
       <c r="L48" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8784,7 +8961,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -8808,9 +8985,12 @@
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8819,7 +8999,7 @@
         <v>44</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -8843,9 +9023,12 @@
       </c>
       <c r="K50" s="9"/>
       <c r="L50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8854,12 +9037,12 @@
         <v>45</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="7" t="n">
-        <v>0.5</v>
+        <v>0.566666</v>
       </c>
       <c r="F51" s="9" t="n">
         <v>0.5</v>
@@ -8878,9 +9061,12 @@
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8889,12 +9075,12 @@
         <v>46</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="7" t="n">
-        <v>0.8</v>
+        <v>0.816666</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>0.8</v>
@@ -8913,9 +9099,12 @@
       </c>
       <c r="K52" s="9"/>
       <c r="L52" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8924,7 +9113,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -8948,9 +9137,12 @@
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8959,7 +9151,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
@@ -8983,9 +9175,12 @@
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8994,7 +9189,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
@@ -9018,9 +9213,12 @@
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9029,7 +9227,7 @@
         <v>50</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
@@ -9053,9 +9251,12 @@
       </c>
       <c r="K56" s="9"/>
       <c r="L56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9064,7 +9265,7 @@
         <v>51</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
@@ -9088,9 +9289,12 @@
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9099,7 +9303,7 @@
         <v>52</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
@@ -9123,9 +9327,12 @@
       </c>
       <c r="K58" s="9"/>
       <c r="L58" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9134,7 +9341,7 @@
         <v>53</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -9158,9 +9365,12 @@
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9169,12 +9379,12 @@
         <v>54</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
       <c r="E60" s="7" t="n">
-        <v>0.5</v>
+        <v>0.566666</v>
       </c>
       <c r="F60" s="9" t="n">
         <v>0.5</v>
@@ -9193,9 +9403,12 @@
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9204,7 +9417,7 @@
         <v>55</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -9228,9 +9441,12 @@
       </c>
       <c r="K61" s="9"/>
       <c r="L61" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9239,7 +9455,7 @@
         <v>56</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
@@ -9263,9 +9479,12 @@
       </c>
       <c r="K62" s="9"/>
       <c r="L62" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9274,7 +9493,7 @@
         <v>57</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
@@ -9298,9 +9517,12 @@
       </c>
       <c r="K63" s="9"/>
       <c r="L63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9309,7 +9531,7 @@
         <v>58</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
@@ -9333,9 +9555,12 @@
       </c>
       <c r="K64" s="9"/>
       <c r="L64" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9344,7 +9569,7 @@
         <v>59</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
@@ -9368,9 +9593,12 @@
       </c>
       <c r="K65" s="9"/>
       <c r="L65" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9379,7 +9607,7 @@
         <v>60</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
@@ -9403,9 +9631,12 @@
       </c>
       <c r="K66" s="9"/>
       <c r="L66" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9414,7 +9645,7 @@
         <v>61</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
@@ -9438,9 +9669,12 @@
       </c>
       <c r="K67" s="9"/>
       <c r="L67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9449,7 +9683,7 @@
         <v>62</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -9473,9 +9707,12 @@
       </c>
       <c r="K68" s="9"/>
       <c r="L68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9484,7 +9721,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
@@ -9508,9 +9745,12 @@
       </c>
       <c r="K69" s="9"/>
       <c r="L69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9519,7 +9759,7 @@
         <v>64</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -9543,9 +9783,12 @@
       </c>
       <c r="K70" s="9"/>
       <c r="L70" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9554,7 +9797,7 @@
         <v>65</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -9578,9 +9821,12 @@
       </c>
       <c r="K71" s="9"/>
       <c r="L71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9589,7 +9835,7 @@
         <v>66</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
@@ -9613,9 +9859,12 @@
       </c>
       <c r="K72" s="9"/>
       <c r="L72" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9624,7 +9873,7 @@
         <v>67</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -9648,9 +9897,12 @@
       </c>
       <c r="K73" s="9"/>
       <c r="L73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9659,7 +9911,7 @@
         <v>68</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
@@ -9683,9 +9935,12 @@
       </c>
       <c r="K74" s="9"/>
       <c r="L74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9694,7 +9949,7 @@
         <v>69</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
@@ -9718,9 +9973,12 @@
       </c>
       <c r="K75" s="9"/>
       <c r="L75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9729,7 +9987,7 @@
         <v>70</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
@@ -9753,9 +10011,12 @@
       </c>
       <c r="K76" s="9"/>
       <c r="L76" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9764,7 +10025,7 @@
         <v>71</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
@@ -9788,9 +10049,12 @@
       </c>
       <c r="K77" s="9"/>
       <c r="L77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9799,7 +10063,7 @@
         <v>72</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
@@ -9823,9 +10087,12 @@
       </c>
       <c r="K78" s="9"/>
       <c r="L78" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9834,7 +10101,7 @@
         <v>73</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
@@ -9858,9 +10125,12 @@
       </c>
       <c r="K79" s="9"/>
       <c r="L79" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9869,7 +10139,7 @@
         <v>74</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
@@ -9893,9 +10163,12 @@
       </c>
       <c r="K80" s="9"/>
       <c r="L80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9904,7 +10177,7 @@
         <v>75</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
@@ -9928,9 +10201,12 @@
       </c>
       <c r="K81" s="9"/>
       <c r="L81" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9939,7 +10215,7 @@
         <v>76</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
@@ -9963,9 +10239,12 @@
       </c>
       <c r="K82" s="9"/>
       <c r="L82" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9974,7 +10253,7 @@
         <v>77</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
@@ -9998,9 +10277,12 @@
       </c>
       <c r="K83" s="9"/>
       <c r="L83" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10009,7 +10291,7 @@
         <v>78</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
@@ -10033,9 +10315,12 @@
       </c>
       <c r="K84" s="9"/>
       <c r="L84" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10044,7 +10329,7 @@
         <v>79</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
@@ -10068,9 +10353,12 @@
       </c>
       <c r="K85" s="9"/>
       <c r="L85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10079,7 +10367,7 @@
         <v>80</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
@@ -10103,9 +10391,12 @@
       </c>
       <c r="K86" s="9"/>
       <c r="L86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10114,7 +10405,7 @@
         <v>81</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
@@ -10138,9 +10429,12 @@
       </c>
       <c r="K87" s="9"/>
       <c r="L87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10149,7 +10443,7 @@
         <v>82</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
@@ -10173,9 +10467,12 @@
       </c>
       <c r="K88" s="9"/>
       <c r="L88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10184,7 +10481,7 @@
         <v>83</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
@@ -10208,9 +10505,12 @@
       </c>
       <c r="K89" s="9"/>
       <c r="L89" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10219,7 +10519,7 @@
         <v>84</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
@@ -10243,9 +10543,12 @@
       </c>
       <c r="K90" s="9"/>
       <c r="L90" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10254,7 +10557,7 @@
         <v>85</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -10278,9 +10581,12 @@
       </c>
       <c r="K91" s="9"/>
       <c r="L91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10289,7 +10595,7 @@
         <v>86</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -10313,9 +10619,12 @@
       </c>
       <c r="K92" s="9"/>
       <c r="L92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10324,7 +10633,7 @@
         <v>87</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -10348,9 +10657,12 @@
       </c>
       <c r="K93" s="9"/>
       <c r="L93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10359,7 +10671,7 @@
         <v>88</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -10383,9 +10695,12 @@
       </c>
       <c r="K94" s="9"/>
       <c r="L94" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10394,7 +10709,7 @@
         <v>89</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
@@ -10418,9 +10733,12 @@
       </c>
       <c r="K95" s="9"/>
       <c r="L95" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10429,7 +10747,7 @@
         <v>90</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
@@ -10453,9 +10771,12 @@
       </c>
       <c r="K96" s="9"/>
       <c r="L96" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10464,7 +10785,7 @@
         <v>91</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
@@ -10488,9 +10809,12 @@
       </c>
       <c r="K97" s="9"/>
       <c r="L97" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10499,7 +10823,7 @@
         <v>92</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
@@ -10523,9 +10847,12 @@
       </c>
       <c r="K98" s="9"/>
       <c r="L98" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10534,7 +10861,7 @@
         <v>93</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
@@ -10558,9 +10885,12 @@
       </c>
       <c r="K99" s="9"/>
       <c r="L99" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10569,7 +10899,7 @@
         <v>94</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
@@ -10593,9 +10923,12 @@
       </c>
       <c r="K100" s="9"/>
       <c r="L100" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10604,7 +10937,7 @@
         <v>95</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
@@ -10628,9 +10961,12 @@
       </c>
       <c r="K101" s="9"/>
       <c r="L101" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10639,12 +10975,12 @@
         <v>96</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c r="E102" s="7" t="n">
-        <v>0.5</v>
+        <v>0.566666</v>
       </c>
       <c r="F102" s="9" t="n">
         <v>0.5</v>
@@ -10663,9 +10999,12 @@
       </c>
       <c r="K102" s="9"/>
       <c r="L102" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10674,7 +11013,7 @@
         <v>97</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
@@ -10698,9 +11037,12 @@
       </c>
       <c r="K103" s="9"/>
       <c r="L103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10709,7 +11051,7 @@
         <v>98</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
@@ -10733,9 +11075,12 @@
       </c>
       <c r="K104" s="9"/>
       <c r="L104" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10744,7 +11089,7 @@
         <v>99</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
@@ -10768,9 +11113,12 @@
       </c>
       <c r="K105" s="9"/>
       <c r="L105" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10779,7 +11127,7 @@
         <v>100</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
@@ -10803,9 +11151,12 @@
       </c>
       <c r="K106" s="9"/>
       <c r="L106" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10832,10 +11183,11 @@
       <c r="T107" s="10"/>
       <c r="U107" s="10"/>
       <c r="V107" s="10"/>
+      <c r="W107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
@@ -10847,7 +11199,7 @@
       <c r="I108" s="11"/>
       <c r="J108" s="11"/>
       <c r="K108" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L108" s="11"/>
       <c r="M108" s="11"/>
@@ -10860,10 +11212,11 @@
       <c r="T108" s="11"/>
       <c r="U108" s="11"/>
       <c r="V108" s="11"/>
+      <c r="W108" s="11"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
@@ -10875,7 +11228,7 @@
       <c r="I109" s="11"/>
       <c r="J109" s="11"/>
       <c r="K109" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L109" s="11"/>
       <c r="M109" s="11"/>
@@ -10888,10 +11241,11 @@
       <c r="T109" s="11"/>
       <c r="U109" s="11"/>
       <c r="V109" s="11"/>
+      <c r="W109" s="11"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -10903,7 +11257,7 @@
       <c r="I110" s="12"/>
       <c r="J110" s="12"/>
       <c r="K110" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L110" s="12"/>
       <c r="M110" s="12"/>
@@ -10916,6 +11270,7 @@
       <c r="T110" s="12"/>
       <c r="U110" s="12"/>
       <c r="V110" s="12"/>
+      <c r="W110" s="12"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="13"/>
@@ -10929,39 +11284,40 @@
       <c r="I111" s="10"/>
       <c r="J111" s="10"/>
       <c r="K111" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L111" s="13"/>
       <c r="M111" s="13"/>
       <c r="N111" s="13"/>
-      <c r="O111" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="P111" s="13" t="s">
+      <c r="O111" s="13"/>
+      <c r="P111" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="Q111" s="13"/>
-      <c r="R111" s="15" t="s">
+      <c r="Q111" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="S111" s="12" t="s">
+      <c r="R111" s="13"/>
+      <c r="S111" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="T111" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="U111" s="10"/>
+      <c r="T111" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="U111" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="V111" s="10"/>
+      <c r="W111" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="226">
     <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="C2:Q2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="C3:Q3"/>
+    <mergeCell ref="R3:V3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B5:D5"/>
@@ -11169,18 +11525,18 @@
     <mergeCell ref="B106:D106"/>
     <mergeCell ref="J106:K106"/>
     <mergeCell ref="A107:J107"/>
-    <mergeCell ref="K107:V107"/>
+    <mergeCell ref="K107:W107"/>
     <mergeCell ref="A108:J108"/>
-    <mergeCell ref="K108:V108"/>
+    <mergeCell ref="K108:W108"/>
     <mergeCell ref="A109:J109"/>
-    <mergeCell ref="K109:V109"/>
+    <mergeCell ref="K109:W109"/>
     <mergeCell ref="A110:J110"/>
-    <mergeCell ref="K110:V110"/>
+    <mergeCell ref="K110:W110"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="D111:J111"/>
-    <mergeCell ref="K111:N111"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="U111:V111"/>
+    <mergeCell ref="K111:O111"/>
+    <mergeCell ref="Q111:R111"/>
+    <mergeCell ref="V111:W111"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
